--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>EgyptAir MS-8223</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9200</v>
+        <v>18204</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9581</v>
+        <v>16711</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-381</v>
+        <v>1493</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6384</v>
+        <v>6929</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13419</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-7035</v>
+        <v>-6490</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7375</v>
+        <v>7856</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13419</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6044</v>
+        <v>-5563</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,552 +653,12 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>29-MAY-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-582</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>11819</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-1600</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>11084</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-2803</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>11084</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-2803</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>11084</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-2803</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-582</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>10687</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>11084</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-397</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-174</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-5931</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-127</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6384</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-5775</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-671</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9102</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-3057</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-582</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>12669</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>510</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-174</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>10248</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-4020</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-127</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>6384</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>10248</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-3864</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-667</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>9102</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>10248</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-1146</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6228</v>
+        <v>6214</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13419</v>
+        <v>13402</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7191</v>
+        <v>-7188</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6929</v>
+        <v>7821</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13419</v>
+        <v>13402</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6490</v>
+        <v>-5581</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -632,33 +632,573 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>flynas XY-568</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8638</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13402</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-4764</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-582</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>11767</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>13402</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-1635</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11076</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-2818</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11076</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-2818</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>11076</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-2818</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-582</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10639</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>11076</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-437</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-5933</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-127</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>7856</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-5563</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="D11" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-5792</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-671</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9075</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-582</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>12612</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-4017</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-3876</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-667</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>9075</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -587,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7821</v>
+        <v>6632</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13402</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5581</v>
+        <v>-6770</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8638</v>
+        <v>7821</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13402</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4764</v>
+        <v>-5581</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11767</v>
+        <v>8258</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13402</v>
+        <v>11076</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1635</v>
+        <v>-2818</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,7 +731,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -767,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11076</v>
+        <v>12147</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2818</v>
+        <v>-5933</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10639</v>
+        <v>6355</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11076</v>
+        <v>12147</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-437</v>
+        <v>-5792</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -902,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5933</v>
+        <v>-3889</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6355</v>
+        <v>6214</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12147</v>
+        <v>10231</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5792</v>
+        <v>-4017</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -968,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-671</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9075</v>
+        <v>6355</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12147</v>
+        <v>10231</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3072</v>
+        <v>-3876</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>EgyptAir MS-659</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12612</v>
+        <v>8258</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12147</v>
+        <v>10231</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>465</v>
+        <v>-1973</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6214</v>
+        <v>5792</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10231</v>
+        <v>21618</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4017</v>
+        <v>-15826</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10231</v>
+        <v>21618</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3876</v>
+        <v>-13360</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-667</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9075</v>
+        <v>8258</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10231</v>
+        <v>21618</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1156</v>
+        <v>-13360</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1193,12 +1202,1497 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-15826</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-13360</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>9061</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-12557</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>9061</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-12557</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>9061</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-12557</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>9061</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-12557</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-9372</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-9372</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-9372</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-762</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-9372</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>13416</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-8202</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>13416</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-8202</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>14501</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-7117</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>14501</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-7117</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-227</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>14839</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-6779</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>14501</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-7117</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>14501</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-7117</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-227</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>14839</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-6779</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-9372</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>12401</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-9217</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>12401</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-9217</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-308</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>9399</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-12219</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-382</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>9399</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-12219</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-386</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>9399</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-12219</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-308</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7398</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-14220</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-382</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>7398</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-14220</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-386</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>7398</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-14220</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-15826</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-15826</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-13360</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-15826</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-15826</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>21618</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-13360</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>6214</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7188</v>
+        <v>-7202</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6632</v>
+        <v>6633</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6770</v>
+        <v>-6783</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>flynas XY-574</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7821</v>
+        <v>9766</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5581</v>
+        <v>-3650</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8258</v>
+        <v>11767</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11076</v>
+        <v>13416</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2818</v>
+        <v>-1649</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12147</v>
+        <v>11076</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5933</v>
+        <v>-2818</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6355</v>
+        <v>10639</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12147</v>
+        <v>11076</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5792</v>
+        <v>-437</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3889</v>
+        <v>-5933</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10231</v>
+        <v>12147</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4017</v>
+        <v>-5792</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10231</v>
+        <v>12147</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3876</v>
+        <v>-3889</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-659</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1973</v>
+        <v>-4017</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5792</v>
+        <v>6355</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21618</v>
+        <v>10231</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-15826</v>
+        <v>-3876</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-659</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21618</v>
+        <v>10231</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-13360</v>
+        <v>-1973</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-13360</v>
+        <v>-15840</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-15826</v>
+        <v>-13374</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1278,10 +1278,10 @@
         <v>8258</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-13360</v>
+        <v>-13374</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9061</v>
+        <v>5792</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-12557</v>
+        <v>-15840</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9061</v>
+        <v>8258</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-12557</v>
+        <v>-13374</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1413,10 +1413,10 @@
         <v>9061</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-12557</v>
+        <v>-12571</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>9061</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-12557</v>
+        <v>-12571</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>12246</v>
+        <v>9061</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-9372</v>
+        <v>-12571</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>12246</v>
+        <v>9061</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9372</v>
+        <v>-12571</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12246</v>
+        <v>13416</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-9372</v>
+        <v>-8216</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12246</v>
+        <v>13416</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-9372</v>
+        <v>-8216</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
         <v>13416</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-8202</v>
+        <v>-8216</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13416</v>
+        <v>12246</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-8202</v>
+        <v>-9386</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>14501</v>
+        <v>13416</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-7117</v>
+        <v>-8216</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>14501</v>
+        <v>13416</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-7117</v>
+        <v>-8216</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14839</v>
+        <v>14501</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-6779</v>
+        <v>-7131</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>14501</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-7117</v>
+        <v>-7131</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14501</v>
+        <v>14839</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-7117</v>
+        <v>-6793</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>14839</v>
+        <v>12246</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-6779</v>
+        <v>-9386</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12246</v>
+        <v>14501</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-9372</v>
+        <v>-7131</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>12401</v>
+        <v>14501</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-9217</v>
+        <v>-7131</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12401</v>
+        <v>12246</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-9217</v>
+        <v>-9386</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-308</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>9399</v>
+        <v>12401</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-12219</v>
+        <v>-9231</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-382</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9399</v>
+        <v>12401</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-12219</v>
+        <v>-9231</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-386</t>
+          <t>flynas XY-572</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9399</v>
+        <v>9766</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-12219</v>
+        <v>-11866</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-308</t>
+          <t>flynas XY-568</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7398</v>
+        <v>9766</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-14220</v>
+        <v>-11866</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-382</t>
+          <t>flynas XY-584</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7398</v>
+        <v>10329</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-14220</v>
+        <v>-11303</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-386</t>
+          <t>Saudia SV-308</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
         <v>7398</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-14220</v>
+        <v>-14234</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>23</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Saudia SV-382</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5792</v>
+        <v>7398</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-15826</v>
+        <v>-14234</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>23</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Saudia SV-386</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5792</v>
+        <v>7398</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-15826</v>
+        <v>-14234</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>23</v>
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-13360</v>
+        <v>-15840</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
         <v>5792</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-15826</v>
+        <v>-15840</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>23</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>21618</v>
+        <v>21632</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-15826</v>
+        <v>-13374</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -2666,33 +2666,123 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-15840</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-15840</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-673</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D51" s="2" t="n">
         <v>8258</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>21618</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-13360</v>
-      </c>
-      <c r="G49" s="2" t="n">
+      <c r="E51" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-13374</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2" t="n">
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10639</v>
+        <v>6214</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11076</v>
+        <v>12147</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-437</v>
+        <v>-5933</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5933</v>
+        <v>-5792</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5792</v>
+        <v>-3889</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12147</v>
+        <v>10231</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3889</v>
+        <v>-4017</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4017</v>
+        <v>-3876</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-667</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6355</v>
+        <v>9075</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3876</v>
+        <v>-1156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-659</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10231</v>
+        <v>21632</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1973</v>
+        <v>-15840</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-15840</v>
+        <v>-13374</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-13374</v>
+        <v>-15840</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-15840</v>
+        <v>-13374</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8258</v>
+        <v>9061</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-13374</v>
+        <v>-12571</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9061</v>
+        <v>12246</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-12571</v>
+        <v>-9386</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13416</v>
+        <v>12246</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8216</v>
+        <v>-9386</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13416</v>
+        <v>12246</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-8216</v>
+        <v>-9386</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13416</v>
+        <v>12246</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-8216</v>
+        <v>-9386</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12246</v>
+        <v>13416</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-9386</v>
+        <v>-8216</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13416</v>
+        <v>14501</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-8216</v>
+        <v>-7131</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14501</v>
+        <v>14839</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-7131</v>
+        <v>-6793</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14839</v>
+        <v>12246</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-6793</v>
+        <v>-9386</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>12246</v>
+        <v>14501</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-9386</v>
+        <v>-7131</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>14501</v>
+        <v>12401</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-7131</v>
+        <v>-9231</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12246</v>
+        <v>12401</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-9386</v>
+        <v>-9231</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>12401</v>
+        <v>12514</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-9231</v>
+        <v>-9118</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>30</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>12401</v>
+        <v>7032</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-9231</v>
+        <v>-14600</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-572</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9766</v>
+        <v>7032</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-11866</v>
+        <v>-14600</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-584</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10329</v>
+        <v>9230</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21632</v>
+        <v>9582</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-11303</v>
+        <v>-352</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>40</v>
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-386</t>
+          <t>flynas XY-590</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7398</v>
+        <v>9766</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-14234</v>
+        <v>-11866</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6633</v>
+        <v>6630</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>13416</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6783</v>
+        <v>-6786</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-574</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9766</v>
+        <v>8526</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13416</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3650</v>
+        <v>-4890</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11767</v>
+        <v>8258</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13416</v>
+        <v>12147</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1649</v>
+        <v>-3889</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11076</v>
+        <v>12147</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2818</v>
+        <v>-3889</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11076</v>
+        <v>12147</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2818</v>
+        <v>-3889</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12147</v>
+        <v>11076</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5933</v>
+        <v>-2818</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12147</v>
+        <v>11076</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5792</v>
+        <v>-2818</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3889</v>
+        <v>-5933</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10231</v>
+        <v>12147</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4017</v>
+        <v>-5792</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10231</v>
+        <v>12147</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3876</v>
+        <v>-3889</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-667</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9075</v>
+        <v>6214</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>10231</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1156</v>
+        <v>-4017</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5792</v>
+        <v>6355</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21632</v>
+        <v>10231</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-15840</v>
+        <v>-3876</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-667</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8258</v>
+        <v>9075</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21632</v>
+        <v>10231</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-13374</v>
+        <v>-1156</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-13374</v>
+        <v>-15840</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-15840</v>
+        <v>-13374</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9061</v>
+        <v>8258</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-12571</v>
+        <v>-13374</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9061</v>
+        <v>8258</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-12571</v>
+        <v>-13374</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>12246</v>
+        <v>9061</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9386</v>
+        <v>-12571</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12246</v>
+        <v>9061</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-9386</v>
+        <v>-12571</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13416</v>
+        <v>12246</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-8216</v>
+        <v>-9386</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>14501</v>
+        <v>13416</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-7131</v>
+        <v>-8216</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14501</v>
+        <v>13416</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-7131</v>
+        <v>-8216</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14839</v>
+        <v>14501</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-6793</v>
+        <v>-7131</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12246</v>
+        <v>14501</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-9386</v>
+        <v>-7131</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>14501</v>
+        <v>14839</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-7131</v>
+        <v>-6793</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>14501</v>
+        <v>12246</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-7131</v>
+        <v>-9386</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>12401</v>
+        <v>14501</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-9231</v>
+        <v>-7131</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12401</v>
+        <v>14501</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-9231</v>
+        <v>-7131</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>12514</v>
+        <v>12401</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-9118</v>
+        <v>-9231</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>30</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7032</v>
+        <v>12401</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-14600</v>
+        <v>-9231</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7032</v>
+        <v>12514</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-14600</v>
+        <v>-9118</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>flynas XY-572</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9766</v>
+        <v>7032</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-11866</v>
+        <v>-14600</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>flynas XY-568</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9230</v>
+        <v>7032</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>9582</v>
+        <v>21632</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-352</v>
+        <v>-14600</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-308</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7398</v>
+        <v>7032</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-14234</v>
+        <v>-14600</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-382</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7398</v>
+        <v>9230</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21632</v>
+        <v>9582</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-14234</v>
+        <v>-352</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-590</t>
+          <t>flynas XY-572</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>flynas XY-590</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5792</v>
+        <v>9766</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-15840</v>
+        <v>-11866</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flynas XY-578</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5792</v>
+        <v>9766</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-15840</v>
+        <v>-11866</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>8258</v>
+        <v>5792</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-13374</v>
+        <v>-15840</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5792</v>
+        <v>8258</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>21632</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-15840</v>
+        <v>-13374</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -2756,33 +2756,123 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-15840</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-15840</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-673</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D53" s="2" t="n">
         <v>8258</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F51" s="2" t="n">
+      <c r="E53" s="2" t="n">
+        <v>21632</v>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>-13374</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" s="2" t="n">
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6214</v>
+        <v>5012</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7202</v>
+        <v>-7134</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6630</v>
+        <v>5012</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6786</v>
+        <v>-7134</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8526</v>
+        <v>6184</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4890</v>
+        <v>-5962</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8258</v>
+        <v>5012</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3889</v>
+        <v>-7134</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3889</v>
+        <v>-5962</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-659</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8258</v>
+        <v>8753</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3889</v>
+        <v>-3393</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-176</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11076</v>
+        <v>11057</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2818</v>
+        <v>-4873</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11076</v>
+        <v>11057</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2818</v>
+        <v>-4873</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11076</v>
+        <v>11057</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2818</v>
+        <v>-4719</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6214</v>
+        <v>5012</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12147</v>
+        <v>7930</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5933</v>
+        <v>-2918</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6355</v>
+        <v>5752</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12147</v>
+        <v>21640</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5792</v>
+        <v>-15888</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8258</v>
+        <v>8753</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12147</v>
+        <v>21640</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3889</v>
+        <v>-12887</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6214</v>
+        <v>8753</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10231</v>
+        <v>21640</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4017</v>
+        <v>-12887</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6355</v>
+        <v>5752</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10231</v>
+        <v>21640</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3876</v>
+        <v>-15888</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-667</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9075</v>
+        <v>8753</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10231</v>
+        <v>21640</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1156</v>
+        <v>-12887</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5792</v>
+        <v>8753</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-15840</v>
+        <v>-12887</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-13374</v>
+        <v>-15302</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-13374</v>
+        <v>-15302</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8258</v>
+        <v>9563</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-13374</v>
+        <v>-12077</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8258</v>
+        <v>12132</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-13374</v>
+        <v>-9508</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9061</v>
+        <v>12132</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-12571</v>
+        <v>-9508</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9061</v>
+        <v>12132</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-12571</v>
+        <v>-9508</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9061</v>
+        <v>12132</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-12571</v>
+        <v>-9508</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9061</v>
+        <v>13933</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-12571</v>
+        <v>-7707</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12246</v>
+        <v>13933</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-9386</v>
+        <v>-7707</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>12246</v>
+        <v>14506</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-9386</v>
+        <v>-7134</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12246</v>
+        <v>14506</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-9386</v>
+        <v>-7134</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13416</v>
+        <v>14827</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-8216</v>
+        <v>-6813</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13416</v>
+        <v>12132</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-8216</v>
+        <v>-9508</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-663</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13416</v>
+        <v>14506</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-8216</v>
+        <v>-7134</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14501</v>
+        <v>14506</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-7131</v>
+        <v>-7134</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flyadeal F3-764</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14501</v>
+        <v>12132</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-7131</v>
+        <v>-9508</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>14839</v>
+        <v>12397</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-6793</v>
+        <v>-9243</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12246</v>
+        <v>12397</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-9386</v>
+        <v>-9243</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>flynas XY-584</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>14501</v>
+        <v>9675</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-7131</v>
+        <v>-11965</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>flynas XY-570</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>14501</v>
+        <v>10233</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-7131</v>
+        <v>-11407</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>flynas XY-572</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>12401</v>
+        <v>10233</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-9231</v>
+        <v>-11407</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Saudia SV-308</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>12401</v>
+        <v>7343</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-9231</v>
+        <v>-14297</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Saudia SV-382</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>12514</v>
+        <v>7343</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-9118</v>
+        <v>-14297</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-572</t>
+          <t>Saudia SV-386</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7032</v>
+        <v>7343</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-14600</v>
+        <v>-14297</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7032</v>
+        <v>5752</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-14600</v>
+        <v>-15888</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7032</v>
+        <v>5752</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-14600</v>
+        <v>-15888</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-582</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>9230</v>
+        <v>8753</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9582</v>
+        <v>21640</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-352</v>
+        <v>-12887</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-572</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>9766</v>
+        <v>5752</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-11866</v>
+        <v>-15888</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-590</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>9766</v>
+        <v>5752</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-11866</v>
+        <v>-15888</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-578</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>9766</v>
+        <v>8753</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>21632</v>
+        <v>21640</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-11866</v>
+        <v>-12887</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2603,276 +2603,6 @@
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>5792</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>-15840</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>5792</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-15840</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-673</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>8258</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>-13374</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>5792</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>-15840</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>5792</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>-15840</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-673</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>8258</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>21632</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>-13374</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5012</v>
+        <v>7286</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12146</v>
+        <v>16574</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7134</v>
+        <v>-9288</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5012</v>
+        <v>7286</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12146</v>
+        <v>16574</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-7134</v>
+        <v>-9288</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-659</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6184</v>
+        <v>7286</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12146</v>
+        <v>16574</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5962</v>
+        <v>-9288</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5012</v>
+        <v>7755</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12146</v>
+        <v>13289</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-7134</v>
+        <v>-5534</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6184</v>
+        <v>7755</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12146</v>
+        <v>13289</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5962</v>
+        <v>-5534</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-659</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8753</v>
+        <v>8252</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12146</v>
+        <v>13289</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3393</v>
+        <v>-5037</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6184</v>
+        <v>12351</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11057</v>
+        <v>13289</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4873</v>
+        <v>-938</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6184</v>
+        <v>7286</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11057</v>
+        <v>10971</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4873</v>
+        <v>-3685</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6338</v>
+        <v>7286</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11057</v>
+        <v>10971</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4719</v>
+        <v>-3685</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5012</v>
+        <v>7286</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7930</v>
+        <v>10971</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2918</v>
+        <v>-3685</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5752</v>
+        <v>7286</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21640</v>
+        <v>12033</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-15888</v>
+        <v>-4747</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8753</v>
+        <v>8252</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>21640</v>
+        <v>12033</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-12887</v>
+        <v>-3781</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8753</v>
+        <v>8252</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21640</v>
+        <v>12033</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-12887</v>
+        <v>-3781</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5752</v>
+        <v>4954</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-15888</v>
+        <v>-3864</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8753</v>
+        <v>7286</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-12887</v>
+        <v>-1532</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-669</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8753</v>
+        <v>7286</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-12887</v>
+        <v>-1532</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6338</v>
+        <v>4954</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-15302</v>
+        <v>-3864</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6338</v>
+        <v>7286</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-15302</v>
+        <v>-1532</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9563</v>
+        <v>7286</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21640</v>
+        <v>8818</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-12077</v>
+        <v>-1532</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>12132</v>
+        <v>4981</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21640</v>
+        <v>8335</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-9508</v>
+        <v>-3354</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>12132</v>
+        <v>7286</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21640</v>
+        <v>8335</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9508</v>
+        <v>-1049</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>flynas XY-582</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>12132</v>
+        <v>9039</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21640</v>
+        <v>8335</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-9508</v>
+        <v>704</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>40</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-762</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>12132</v>
+        <v>4954</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>21640</v>
+        <v>7852</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9508</v>
+        <v>-2898</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13933</v>
+        <v>4981</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>21640</v>
+        <v>7852</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-7707</v>
+        <v>-2871</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13933</v>
+        <v>7286</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21640</v>
+        <v>7852</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-7707</v>
+        <v>-566</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>14506</v>
+        <v>6085</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-7134</v>
+        <v>-15388</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>14506</v>
+        <v>7286</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-7134</v>
+        <v>-14187</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>14827</v>
+        <v>7286</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-6813</v>
+        <v>-14187</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12132</v>
+        <v>7286</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-9508</v>
+        <v>-14187</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14506</v>
+        <v>7755</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-7134</v>
+        <v>-13718</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14506</v>
+        <v>7755</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-7134</v>
+        <v>-13718</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,28 +1946,28 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12132</v>
+        <v>7755</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-9508</v>
+        <v>-13718</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>12397</v>
+        <v>7755</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-9243</v>
+        <v>-13718</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12397</v>
+        <v>8252</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-9243</v>
+        <v>-13221</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-584</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9675</v>
+        <v>13248</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-11965</v>
+        <v>-8225</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-570</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10233</v>
+        <v>13248</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-11407</v>
+        <v>-8225</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-572</t>
+          <t>EgyptAir MS-663</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10233</v>
+        <v>13248</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-11407</v>
+        <v>-8225</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-308</t>
+          <t>flyadeal F3-762</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7343</v>
+        <v>11992</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-14297</v>
+        <v>-9481</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,28 +2261,28 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-382</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7343</v>
+        <v>13248</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-14297</v>
+        <v>-8225</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-386</t>
+          <t>EgyptAir MS-665</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7343</v>
+        <v>13248</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-14297</v>
+        <v>-8225</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>5752</v>
+        <v>14379</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-15888</v>
+        <v>-7094</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5752</v>
+        <v>14379</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-15888</v>
+        <v>-7094</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>8753</v>
+        <v>14655</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-12887</v>
+        <v>-6818</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,28 +2486,28 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5752</v>
+        <v>11992</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-15888</v>
+        <v>-9481</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5752</v>
+        <v>14379</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>21640</v>
+        <v>21473</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-15888</v>
+        <v>-7094</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,43 +2566,628 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>14379</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-7094</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>6886</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-14587</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>6886</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-14587</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-764</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>6886</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-14587</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-582</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>9039</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>9467</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-428</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-308</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>7093</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-14380</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-382</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>7093</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-14380</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-568</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9563</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-11910</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-15774</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-15774</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-673</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>8156</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-13317</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>29-SEP-26</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SM-453</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-15774</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-15774</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-453</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-673</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
-        <v>8753</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>21640</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>-12887</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="D60" s="2" t="n">
+        <v>8156</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>21473</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-13317</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
